--- a/data/exports/predictions/uk49s_predictions.xlsx
+++ b/data/exports/predictions/uk49s_predictions.xlsx
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
         <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
         <v>38</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -561,10 +561,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1077.5479</v>
+        <v>1081.9381</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -576,7 +576,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>41</v>
       </c>
       <c r="H3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="J3" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -629,10 +629,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1077.4944</v>
+        <v>1081.705</v>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -694,10 +694,10 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1075.9942</v>
+        <v>1079.1709</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.95</v>
+        <v>94.91</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -723,25 +723,25 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
+        <v>44</v>
+      </c>
+      <c r="H5" t="n">
         <v>45</v>
       </c>
-      <c r="H5" t="n">
-        <v>46</v>
-      </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J5" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -759,10 +759,10 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1072.7218</v>
+        <v>1073.9664</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.84</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J6" t="n">
         <v>163</v>
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1070.2459</v>
+        <v>1073.1462</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.76000000000001</v>
+        <v>94.72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -850,28 +850,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I7" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J7" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -886,13 +886,13 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1069.2212</v>
+        <v>1072.1509</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.73</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H8" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I8" t="n">
         <v>48</v>
       </c>
       <c r="J8" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -954,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1068.4488</v>
+        <v>1071.236</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.7</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -980,28 +980,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -1016,13 +1016,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1066.1999</v>
+        <v>1069.606</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.63</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -1045,28 +1045,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
         <v>13</v>
-      </c>
-      <c r="E10" t="n">
-        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -1081,13 +1081,13 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1065.8605</v>
+        <v>1069.3865</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.62</v>
+        <v>94.59</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -1149,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1065.8568</v>
+        <v>1067.1782</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.62</v>
+        <v>94.52</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H12" t="n">
         <v>49</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -1211,10 +1211,10 @@
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1067.6419</v>
+        <v>1072.3153</v>
       </c>
       <c r="Q12" t="n">
         <v>95</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H13" t="n">
         <v>49</v>
       </c>
       <c r="I13" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J13" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1276,13 +1276,13 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1062.9253</v>
+        <v>1068.5014</v>
       </c>
       <c r="Q13" t="n">
-        <v>94.84999999999999</v>
+        <v>94.88</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1308,25 +1308,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H14" t="n">
         <v>49</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1344,10 +1344,10 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>1061.2692</v>
+        <v>1058.8864</v>
       </c>
       <c r="Q14" t="n">
-        <v>94.79000000000001</v>
+        <v>94.56</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1370,49 +1370,49 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>37</v>
+      </c>
+      <c r="G15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H15" t="n">
+        <v>44</v>
+      </c>
+      <c r="I15" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" t="n">
+        <v>151</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>20</v>
-      </c>
-      <c r="F15" t="n">
-        <v>38</v>
-      </c>
-      <c r="G15" t="n">
-        <v>42</v>
-      </c>
-      <c r="H15" t="n">
-        <v>49</v>
-      </c>
-      <c r="I15" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" t="n">
-        <v>159</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
-        <v>1057.8145</v>
+        <v>1057.0435</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.68000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G16" t="n">
         <v>38</v>
@@ -1453,10 +1453,10 @@
         <v>49</v>
       </c>
       <c r="I16" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J16" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1471,13 +1471,13 @@
         <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1057.0431</v>
+        <v>1056.7845</v>
       </c>
       <c r="Q16" t="n">
-        <v>94.65000000000001</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H17" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I17" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -1536,13 +1536,13 @@
         <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1053.5765</v>
+        <v>1056.0348</v>
       </c>
       <c r="Q17" t="n">
-        <v>94.54000000000001</v>
+        <v>94.47</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
         <v>24</v>
@@ -1577,16 +1577,16 @@
         <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H18" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
@@ -1604,10 +1604,10 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>1052.9285</v>
+        <v>1054.9495</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.52</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1633,25 +1633,25 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H19" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I19" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J19" t="n">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -1666,13 +1666,13 @@
         <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>1052.3426</v>
+        <v>1054.684</v>
       </c>
       <c r="Q19" t="n">
-        <v>94.5</v>
+        <v>94.42</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" t="n">
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H20" t="n">
         <v>49</v>
       </c>
       <c r="I20" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J20" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1052.3301</v>
+        <v>1053.3476</v>
       </c>
       <c r="Q20" t="n">
-        <v>94.5</v>
+        <v>94.38</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1763,10 +1763,10 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>38</v>
@@ -1778,10 +1778,10 @@
         <v>49</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
@@ -1796,13 +1796,13 @@
         <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1051.8791</v>
+        <v>1053.0949</v>
       </c>
       <c r="Q21" t="n">
-        <v>94.48</v>
+        <v>94.37</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -1936,28 +1936,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
         <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
         <v>38</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -1972,10 +1972,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1077.5479</v>
+        <v>1081.9381</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2001,28 +2001,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>41</v>
       </c>
       <c r="H3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="J3" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2040,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1077.4944</v>
+        <v>1081.705</v>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2105,10 +2105,10 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1075.9942</v>
+        <v>1079.1709</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.95</v>
+        <v>94.91</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2134,25 +2134,25 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
+        <v>44</v>
+      </c>
+      <c r="H5" t="n">
         <v>45</v>
       </c>
-      <c r="H5" t="n">
-        <v>46</v>
-      </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J5" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -2170,10 +2170,10 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1072.7218</v>
+        <v>1073.9664</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.84</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2196,25 +2196,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H6" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="J6" t="n">
         <v>163</v>
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1070.2459</v>
+        <v>1073.1462</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.76000000000001</v>
+        <v>94.72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2261,28 +2261,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I7" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J7" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -2297,13 +2297,13 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1069.2212</v>
+        <v>1072.1509</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.73</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2326,28 +2326,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H8" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I8" t="n">
         <v>48</v>
       </c>
       <c r="J8" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1068.4488</v>
+        <v>1071.236</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.7</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2391,28 +2391,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -2427,13 +2427,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1066.1999</v>
+        <v>1069.606</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.63</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2456,28 +2456,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
         <v>13</v>
-      </c>
-      <c r="E10" t="n">
-        <v>20</v>
       </c>
       <c r="F10" t="n">
         <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -2492,13 +2492,13 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1065.8605</v>
+        <v>1069.3865</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.62</v>
+        <v>94.59</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -2560,10 +2560,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1065.8568</v>
+        <v>1067.1782</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.62</v>
+        <v>94.52</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:17</t>
+          <t>2026-05-24 05:28:01</t>
         </is>
       </c>
     </row>
@@ -2697,28 +2697,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
         <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -2733,10 +2733,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1067.6419</v>
+        <v>1072.3153</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -2762,28 +2762,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J3" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2798,13 +2798,13 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1062.9253</v>
+        <v>1068.5014</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.84999999999999</v>
+        <v>94.88</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -2830,25 +2830,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H4" t="n">
         <v>49</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J4" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2866,10 +2866,10 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1061.2692</v>
+        <v>1058.8864</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.79000000000001</v>
+        <v>94.56</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -2892,49 +2892,49 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G5" t="n">
+        <v>38</v>
+      </c>
+      <c r="H5" t="n">
+        <v>44</v>
+      </c>
+      <c r="I5" t="n">
+        <v>19</v>
+      </c>
+      <c r="J5" t="n">
+        <v>151</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F5" t="n">
-        <v>38</v>
-      </c>
-      <c r="G5" t="n">
-        <v>42</v>
-      </c>
-      <c r="H5" t="n">
-        <v>49</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>159</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>1057.8145</v>
+        <v>1057.0435</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.68000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -2957,16 +2957,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
         <v>38</v>
@@ -2975,10 +2975,10 @@
         <v>49</v>
       </c>
       <c r="I6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -2993,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1057.0431</v>
+        <v>1056.7845</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.65000000000001</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -3022,28 +3022,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I7" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -3058,13 +3058,13 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1053.5765</v>
+        <v>1056.0348</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.54000000000001</v>
+        <v>94.47</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -3087,10 +3087,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
@@ -3099,16 +3099,16 @@
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H8" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J8" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -3126,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1052.9285</v>
+        <v>1054.9495</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.52</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -3155,25 +3155,25 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J9" t="n">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -3188,13 +3188,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1052.3426</v>
+        <v>1054.684</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.5</v>
+        <v>94.42</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -3217,28 +3217,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H10" t="n">
         <v>49</v>
       </c>
       <c r="I10" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J10" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1052.3301</v>
+        <v>1053.3476</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.5</v>
+        <v>94.38</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>
@@ -3285,10 +3285,10 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
         <v>38</v>
@@ -3300,10 +3300,10 @@
         <v>49</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -3318,13 +3318,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1051.8791</v>
+        <v>1053.0949</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.48</v>
+        <v>94.37</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:16:22</t>
+          <t>2026-05-24 05:28:04</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/uk49s_predictions.xlsx
+++ b/data/exports/predictions/uk49s_predictions.xlsx
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -564,7 +564,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1081.9381</v>
+        <v>1081.0558</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -576,7 +576,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I3" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -626,10 +626,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1081.705</v>
+        <v>1080.6296</v>
       </c>
       <c r="Q3" t="n">
         <v>94.98999999999999</v>
@@ -641,7 +641,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H4" t="n">
         <v>40</v>
       </c>
-      <c r="H4" t="n">
-        <v>45</v>
-      </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -691,13 +691,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1079.1709</v>
+        <v>1077.9164</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.91</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -720,28 +720,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
         <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -756,13 +756,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1073.9664</v>
+        <v>1072.1981</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.73999999999999</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -785,25 +785,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
+        <v>41</v>
+      </c>
+      <c r="H6" t="n">
         <v>43</v>
       </c>
-      <c r="H6" t="n">
-        <v>45</v>
-      </c>
       <c r="I6" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>163</v>
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1073.1462</v>
+        <v>1071.2451</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.72</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -886,10 +886,10 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1072.1509</v>
+        <v>1071.2342</v>
       </c>
       <c r="Q7" t="n">
         <v>94.68000000000001</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J8" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -954,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1071.236</v>
+        <v>1068.9323</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.65000000000001</v>
+        <v>94.61</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -980,46 +980,46 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>49</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" t="n">
+        <v>165</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" t="n">
-        <v>38</v>
-      </c>
-      <c r="H9" t="n">
-        <v>44</v>
-      </c>
-      <c r="I9" t="n">
-        <v>27</v>
-      </c>
-      <c r="J9" t="n">
-        <v>127</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
-        <v>1069.606</v>
+        <v>1068.605</v>
       </c>
       <c r="Q9" t="n">
         <v>94.59999999999999</v>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -1045,28 +1045,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -1081,13 +1081,13 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1069.3865</v>
+        <v>1068.585</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.59</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J11" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -1146,13 +1146,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1067.1782</v>
+        <v>1067.7332</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.52</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -1178,25 +1178,25 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
+        <v>37</v>
+      </c>
+      <c r="G12" t="n">
         <v>38</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>44</v>
       </c>
-      <c r="H12" t="n">
-        <v>49</v>
-      </c>
       <c r="I12" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -1211,10 +1211,10 @@
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>1072.3153</v>
+        <v>1060.4893</v>
       </c>
       <c r="Q12" t="n">
         <v>95</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>38</v>
+      </c>
+      <c r="H13" t="n">
         <v>39</v>
       </c>
-      <c r="G13" t="n">
-        <v>44</v>
-      </c>
-      <c r="H13" t="n">
-        <v>49</v>
-      </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J13" t="n">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1276,13 +1276,13 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>1068.5014</v>
+        <v>1059.5504</v>
       </c>
       <c r="Q13" t="n">
-        <v>94.88</v>
+        <v>94.97</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H14" t="n">
+        <v>44</v>
+      </c>
+      <c r="I14" t="n">
         <v>49</v>
       </c>
-      <c r="I14" t="n">
-        <v>23</v>
-      </c>
       <c r="J14" t="n">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1341,13 +1341,13 @@
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1058.8864</v>
+        <v>1058.349</v>
       </c>
       <c r="Q14" t="n">
-        <v>94.56</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1373,25 +1373,25 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>24</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
@@ -1409,10 +1409,10 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>1057.0435</v>
+        <v>1057.9318</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.5</v>
+        <v>94.92</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
         <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I16" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1471,13 +1471,13 @@
         <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>1056.7845</v>
+        <v>1057.6968</v>
       </c>
       <c r="Q16" t="n">
-        <v>94.48999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -1509,19 +1509,19 @@
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H17" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -1536,13 +1536,13 @@
         <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>1056.0348</v>
+        <v>1057.1423</v>
       </c>
       <c r="Q17" t="n">
-        <v>94.47</v>
+        <v>94.89</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
@@ -1601,13 +1601,13 @@
         <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1054.9495</v>
+        <v>1056.4185</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.43000000000001</v>
+        <v>94.87</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1633,25 +1633,25 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H19" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I19" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -1666,13 +1666,13 @@
         <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1054.684</v>
+        <v>1055.8227</v>
       </c>
       <c r="Q19" t="n">
-        <v>94.42</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H20" t="n">
         <v>49</v>
       </c>
       <c r="I20" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J20" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1053.3476</v>
+        <v>1055.4751</v>
       </c>
       <c r="Q20" t="n">
-        <v>94.38</v>
+        <v>94.83</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1763,25 +1763,25 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
+        <v>34</v>
+      </c>
+      <c r="G21" t="n">
         <v>38</v>
       </c>
-      <c r="G21" t="n">
-        <v>42</v>
-      </c>
       <c r="H21" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
@@ -1796,13 +1796,13 @@
         <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>1053.0949</v>
+        <v>1054.5217</v>
       </c>
       <c r="Q21" t="n">
-        <v>94.37</v>
+        <v>94.8</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -1936,28 +1936,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -1975,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1081.9381</v>
+        <v>1081.0558</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2001,28 +2001,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I3" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2037,10 +2037,10 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1081.705</v>
+        <v>1080.6296</v>
       </c>
       <c r="Q3" t="n">
         <v>94.98999999999999</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2066,28 +2066,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
+        <v>38</v>
+      </c>
+      <c r="H4" t="n">
         <v>40</v>
       </c>
-      <c r="H4" t="n">
-        <v>45</v>
-      </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2102,13 +2102,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1079.1709</v>
+        <v>1077.9164</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.91</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2131,28 +2131,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
         <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -2167,13 +2167,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1073.9664</v>
+        <v>1072.1981</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.73999999999999</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2196,25 +2196,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G6" t="n">
+        <v>41</v>
+      </c>
+      <c r="H6" t="n">
         <v>43</v>
       </c>
-      <c r="H6" t="n">
-        <v>45</v>
-      </c>
       <c r="I6" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>163</v>
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1073.1462</v>
+        <v>1071.2451</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.72</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2264,25 +2264,25 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I7" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -2297,10 +2297,10 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1072.1509</v>
+        <v>1071.2342</v>
       </c>
       <c r="Q7" t="n">
         <v>94.68000000000001</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2326,28 +2326,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J8" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1071.236</v>
+        <v>1068.9323</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.65000000000001</v>
+        <v>94.61</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2391,46 +2391,46 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>49</v>
+      </c>
+      <c r="I9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J9" t="n">
+        <v>165</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F9" t="n">
-        <v>30</v>
-      </c>
-      <c r="G9" t="n">
-        <v>38</v>
-      </c>
-      <c r="H9" t="n">
-        <v>44</v>
-      </c>
-      <c r="I9" t="n">
-        <v>27</v>
-      </c>
-      <c r="J9" t="n">
-        <v>127</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
-        <v>1069.606</v>
+        <v>1068.605</v>
       </c>
       <c r="Q9" t="n">
         <v>94.59999999999999</v>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2456,28 +2456,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -2492,13 +2492,13 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1069.3865</v>
+        <v>1068.585</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.59</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H11" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J11" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -2557,13 +2557,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1067.1782</v>
+        <v>1067.7332</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.52</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:01</t>
+          <t>2026-05-25 14:24:58</t>
         </is>
       </c>
     </row>
@@ -2700,25 +2700,25 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G2" t="n">
         <v>38</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>44</v>
       </c>
-      <c r="H2" t="n">
-        <v>49</v>
-      </c>
       <c r="I2" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J2" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -2733,10 +2733,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1072.3153</v>
+        <v>1060.4893</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -2762,28 +2762,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
+        <v>25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>38</v>
+      </c>
+      <c r="H3" t="n">
         <v>39</v>
       </c>
-      <c r="G3" t="n">
-        <v>44</v>
-      </c>
-      <c r="H3" t="n">
-        <v>49</v>
-      </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="J3" t="n">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2798,13 +2798,13 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>1068.5014</v>
+        <v>1059.5504</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.88</v>
+        <v>94.97</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -2827,28 +2827,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H4" t="n">
+        <v>44</v>
+      </c>
+      <c r="I4" t="n">
         <v>49</v>
       </c>
-      <c r="I4" t="n">
-        <v>23</v>
-      </c>
       <c r="J4" t="n">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2863,13 +2863,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1058.8864</v>
+        <v>1058.349</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.56</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -2895,25 +2895,25 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J5" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -2931,10 +2931,10 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1057.0435</v>
+        <v>1057.9318</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.5</v>
+        <v>94.92</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -2957,28 +2957,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -2993,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1056.7845</v>
+        <v>1057.6968</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.48999999999999</v>
+        <v>94.91</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3031,19 +3031,19 @@
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -3058,13 +3058,13 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1056.0348</v>
+        <v>1057.1423</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.47</v>
+        <v>94.89</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -3087,28 +3087,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -3123,13 +3123,13 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1054.9495</v>
+        <v>1056.4185</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.43000000000001</v>
+        <v>94.87</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -3155,25 +3155,25 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I9" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -3188,13 +3188,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1054.684</v>
+        <v>1055.8227</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.42</v>
+        <v>94.84999999999999</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -3217,28 +3217,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H10" t="n">
         <v>49</v>
       </c>
       <c r="I10" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="J10" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -3256,10 +3256,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1053.3476</v>
+        <v>1055.4751</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.38</v>
+        <v>94.83</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>
@@ -3285,25 +3285,25 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
+        <v>34</v>
+      </c>
+      <c r="G11" t="n">
         <v>38</v>
       </c>
-      <c r="G11" t="n">
-        <v>42</v>
-      </c>
       <c r="H11" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -3318,13 +3318,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1053.0949</v>
+        <v>1054.5217</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.37</v>
+        <v>94.8</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:28:04</t>
+          <t>2026-05-25 14:25:00</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/uk49s_predictions.xlsx
+++ b/data/exports/predictions/uk49s_predictions.xlsx
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -561,10 +561,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1081.0558</v>
+        <v>1085.3362</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -576,7 +576,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
         <v>9</v>
       </c>
-      <c r="D3" t="n">
-        <v>16</v>
-      </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>44</v>
@@ -608,10 +608,10 @@
         <v>45</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J3" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -629,10 +629,10 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1080.6296</v>
+        <v>1083.0127</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.98999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -694,10 +694,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1077.9164</v>
+        <v>1080.4242</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.90000000000001</v>
+        <v>94.84</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -720,28 +720,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G5" t="n">
+        <v>41</v>
+      </c>
+      <c r="H5" t="n">
+        <v>44</v>
+      </c>
+      <c r="I5" t="n">
         <v>7</v>
       </c>
-      <c r="E5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G5" t="n">
-        <v>38</v>
-      </c>
-      <c r="H5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
       <c r="J5" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -759,10 +759,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1072.1981</v>
+        <v>1077.5757</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.70999999999999</v>
+        <v>94.75</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
@@ -797,16 +797,16 @@
         <v>33</v>
       </c>
       <c r="G6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H6" t="n">
         <v>41</v>
       </c>
-      <c r="H6" t="n">
-        <v>43</v>
-      </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -821,13 +821,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1071.2451</v>
+        <v>1076.7101</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.68000000000001</v>
+        <v>94.72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -853,25 +853,25 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
         <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J7" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -886,13 +886,13 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1071.2342</v>
+        <v>1075.9632</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.68000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>19</v>
@@ -924,19 +924,19 @@
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" t="n">
         <v>40</v>
       </c>
-      <c r="H8" t="n">
-        <v>45</v>
-      </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -951,13 +951,13 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1068.9323</v>
+        <v>1075.7471</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.61</v>
+        <v>94.69</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -980,28 +980,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>41</v>
+      </c>
+      <c r="I9" t="n">
         <v>48</v>
       </c>
-      <c r="H9" t="n">
-        <v>49</v>
-      </c>
-      <c r="I9" t="n">
-        <v>13</v>
-      </c>
       <c r="J9" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -1016,13 +1016,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1068.605</v>
+        <v>1074.3567</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.59999999999999</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -1045,28 +1045,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
+        <v>38</v>
+      </c>
+      <c r="H10" t="n">
         <v>40</v>
       </c>
-      <c r="H10" t="n">
-        <v>45</v>
-      </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J10" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -1084,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1068.585</v>
+        <v>1072.873</v>
       </c>
       <c r="Q10" t="n">
         <v>94.59999999999999</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>39</v>
       </c>
       <c r="H11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I11" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1067.7332</v>
+        <v>1071.9097</v>
       </c>
       <c r="Q11" t="n">
         <v>94.56999999999999</v>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
+        <v>42</v>
+      </c>
+      <c r="H12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I12" t="n">
         <v>38</v>
       </c>
-      <c r="H12" t="n">
-        <v>44</v>
-      </c>
-      <c r="I12" t="n">
-        <v>20</v>
-      </c>
       <c r="J12" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -1211,10 +1211,10 @@
         <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1060.4893</v>
+        <v>1075.2819</v>
       </c>
       <c r="Q12" t="n">
         <v>95</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1243,25 +1243,25 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H13" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1276,13 +1276,13 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1059.5504</v>
+        <v>1073.5418</v>
       </c>
       <c r="Q13" t="n">
-        <v>94.97</v>
+        <v>94.94</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1308,25 +1308,25 @@
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39</v>
+      </c>
+      <c r="H14" t="n">
+        <v>45</v>
+      </c>
+      <c r="I14" t="n">
         <v>25</v>
       </c>
-      <c r="G14" t="n">
-        <v>38</v>
-      </c>
-      <c r="H14" t="n">
-        <v>44</v>
-      </c>
-      <c r="I14" t="n">
-        <v>49</v>
-      </c>
       <c r="J14" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1344,10 +1344,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1058.349</v>
+        <v>1067.6137</v>
       </c>
       <c r="Q14" t="n">
-        <v>94.93000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
         <v>139</v>
@@ -1406,13 +1406,13 @@
         <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1057.9318</v>
+        <v>1064.0483</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.92</v>
+        <v>94.63</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1438,25 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1471,13 +1471,13 @@
         <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1057.6968</v>
+        <v>1063.6903</v>
       </c>
       <c r="Q16" t="n">
-        <v>94.91</v>
+        <v>94.62</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J17" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -1539,10 +1539,10 @@
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>1057.1423</v>
+        <v>1063.5943</v>
       </c>
       <c r="Q17" t="n">
-        <v>94.89</v>
+        <v>94.62</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
+        <v>40</v>
+      </c>
+      <c r="H18" t="n">
         <v>42</v>
       </c>
-      <c r="H18" t="n">
-        <v>46</v>
-      </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
@@ -1601,13 +1601,13 @@
         <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>1056.4185</v>
+        <v>1060.8781</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.87</v>
+        <v>94.53</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1633,25 +1633,25 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H19" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="J19" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -1666,13 +1666,13 @@
         <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>1055.8227</v>
+        <v>1060.6875</v>
       </c>
       <c r="Q19" t="n">
-        <v>94.84999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1698,25 +1698,25 @@
         <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G20" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H20" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I20" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
@@ -1731,13 +1731,13 @@
         <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>1055.4751</v>
+        <v>1058.9128</v>
       </c>
       <c r="Q20" t="n">
-        <v>94.83</v>
+        <v>94.47</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1763,25 +1763,25 @@
         <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H21" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
@@ -1796,13 +1796,13 @@
         <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1054.5217</v>
+        <v>1058.2904</v>
       </c>
       <c r="Q21" t="n">
-        <v>94.8</v>
+        <v>94.45</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -1936,28 +1936,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>24</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -1972,10 +1972,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1081.0558</v>
+        <v>1085.3362</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2001,16 +2001,16 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
         <v>9</v>
       </c>
-      <c r="D3" t="n">
-        <v>16</v>
-      </c>
       <c r="E3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>44</v>
@@ -2019,10 +2019,10 @@
         <v>45</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J3" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2040,10 +2040,10 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1080.6296</v>
+        <v>1083.0127</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.98999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2066,28 +2066,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2105,10 +2105,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1077.9164</v>
+        <v>1080.4242</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.90000000000001</v>
+        <v>94.84</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2131,28 +2131,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
+        <v>16</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G5" t="n">
+        <v>41</v>
+      </c>
+      <c r="H5" t="n">
+        <v>44</v>
+      </c>
+      <c r="I5" t="n">
         <v>7</v>
       </c>
-      <c r="E5" t="n">
-        <v>24</v>
-      </c>
-      <c r="F5" t="n">
-        <v>26</v>
-      </c>
-      <c r="G5" t="n">
-        <v>38</v>
-      </c>
-      <c r="H5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
       <c r="J5" t="n">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -2170,10 +2170,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1072.1981</v>
+        <v>1077.5757</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.70999999999999</v>
+        <v>94.75</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
@@ -2208,16 +2208,16 @@
         <v>33</v>
       </c>
       <c r="G6" t="n">
+        <v>38</v>
+      </c>
+      <c r="H6" t="n">
         <v>41</v>
       </c>
-      <c r="H6" t="n">
-        <v>43</v>
-      </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -2232,13 +2232,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1071.2451</v>
+        <v>1076.7101</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.68000000000001</v>
+        <v>94.72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2264,25 +2264,25 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
         <v>41</v>
       </c>
       <c r="H7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J7" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -2297,13 +2297,13 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1071.2342</v>
+        <v>1075.9632</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.68000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>19</v>
@@ -2335,19 +2335,19 @@
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H8" t="n">
         <v>40</v>
       </c>
-      <c r="H8" t="n">
-        <v>45</v>
-      </c>
       <c r="I8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -2362,13 +2362,13 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1068.9323</v>
+        <v>1075.7471</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.61</v>
+        <v>94.69</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2391,28 +2391,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H9" t="n">
+        <v>41</v>
+      </c>
+      <c r="I9" t="n">
         <v>48</v>
       </c>
-      <c r="H9" t="n">
-        <v>49</v>
-      </c>
-      <c r="I9" t="n">
-        <v>13</v>
-      </c>
       <c r="J9" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -2427,13 +2427,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1068.605</v>
+        <v>1074.3567</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.59999999999999</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2456,28 +2456,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
+        <v>38</v>
+      </c>
+      <c r="H10" t="n">
         <v>40</v>
       </c>
-      <c r="H10" t="n">
-        <v>45</v>
-      </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J10" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1068.585</v>
+        <v>1072.873</v>
       </c>
       <c r="Q10" t="n">
         <v>94.59999999999999</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>39</v>
       </c>
       <c r="H11" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I11" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -2560,7 +2560,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1067.7332</v>
+        <v>1071.9097</v>
       </c>
       <c r="Q11" t="n">
         <v>94.56999999999999</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:58</t>
+          <t>2026-05-26 14:15:45</t>
         </is>
       </c>
     </row>
@@ -2697,28 +2697,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
+        <v>42</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49</v>
+      </c>
+      <c r="I2" t="n">
         <v>38</v>
       </c>
-      <c r="H2" t="n">
-        <v>44</v>
-      </c>
-      <c r="I2" t="n">
-        <v>20</v>
-      </c>
       <c r="J2" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -2733,10 +2733,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1060.4893</v>
+        <v>1075.2819</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -2765,25 +2765,25 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2798,13 +2798,13 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1059.5504</v>
+        <v>1073.5418</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.97</v>
+        <v>94.94</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -2830,25 +2830,25 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
+        <v>34</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" t="n">
+        <v>45</v>
+      </c>
+      <c r="I4" t="n">
         <v>25</v>
       </c>
-      <c r="G4" t="n">
-        <v>38</v>
-      </c>
-      <c r="H4" t="n">
-        <v>44</v>
-      </c>
-      <c r="I4" t="n">
-        <v>49</v>
-      </c>
       <c r="J4" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1058.349</v>
+        <v>1067.6137</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.93000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -2895,22 +2895,22 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
         <v>139</v>
@@ -2928,13 +2928,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1057.9318</v>
+        <v>1064.0483</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.92</v>
+        <v>94.63</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -2960,25 +2960,25 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -2993,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1057.6968</v>
+        <v>1063.6903</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.91</v>
+        <v>94.62</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -3022,28 +3022,28 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
         <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -3061,10 +3061,10 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1057.1423</v>
+        <v>1063.5943</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.89</v>
+        <v>94.62</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -3087,28 +3087,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" t="n">
         <v>42</v>
       </c>
-      <c r="H8" t="n">
-        <v>46</v>
-      </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -3123,13 +3123,13 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1056.4185</v>
+        <v>1060.8781</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.87</v>
+        <v>94.53</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -3155,25 +3155,25 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H9" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="J9" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -3188,13 +3188,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1055.8227</v>
+        <v>1060.6875</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.84999999999999</v>
+        <v>94.52</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -3220,25 +3220,25 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="H10" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="I10" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="J10" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -3253,13 +3253,13 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1055.4751</v>
+        <v>1058.9128</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.83</v>
+        <v>94.47</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>
@@ -3285,25 +3285,25 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H11" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -3318,13 +3318,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1054.5217</v>
+        <v>1058.2904</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.8</v>
+        <v>94.45</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:25:00</t>
+          <t>2026-05-26 14:15:47</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/uk49s_predictions.xlsx
+++ b/data/exports/predictions/uk49s_predictions.xlsx
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -561,10 +561,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>1085.3362</v>
+        <v>1085.8226</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -576,7 +576,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
         <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -626,13 +626,13 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1083.0127</v>
+        <v>1085.7483</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.93000000000001</v>
+        <v>95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H4" t="n">
         <v>45</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -691,13 +691,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>1080.4242</v>
+        <v>1085.0111</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.84</v>
+        <v>94.97</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -720,28 +720,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J5" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -756,13 +756,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1077.5757</v>
+        <v>1084.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.75</v>
+        <v>94.95</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -821,13 +821,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1076.7101</v>
+        <v>1082.4713</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.72</v>
+        <v>94.89</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -850,28 +850,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
+        <v>26</v>
+      </c>
+      <c r="G7" t="n">
         <v>31</v>
       </c>
-      <c r="G7" t="n">
-        <v>41</v>
-      </c>
       <c r="H7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I7" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -889,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1075.9632</v>
+        <v>1080.4438</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.7</v>
+        <v>94.83</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -954,10 +954,10 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1075.7471</v>
+        <v>1080.0368</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.69</v>
+        <v>94.81</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -980,28 +980,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J9" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -1019,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1074.3567</v>
+        <v>1079.3732</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.65000000000001</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -1045,28 +1045,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" t="n">
         <v>19</v>
       </c>
-      <c r="E10" t="n">
-        <v>24</v>
-      </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I10" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -1084,10 +1084,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1072.873</v>
+        <v>1079.2948</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.59999999999999</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
         <v>40</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="J11" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -1149,10 +1149,10 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1071.9097</v>
+        <v>1078.208</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.56999999999999</v>
+        <v>94.75</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H12" t="n">
         <v>49</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1075.2819</v>
+        <v>1077.37</v>
       </c>
       <c r="Q12" t="n">
         <v>95</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>24</v>
       </c>
       <c r="F13" t="n">
+        <v>31</v>
+      </c>
+      <c r="G13" t="n">
         <v>34</v>
-      </c>
-      <c r="G13" t="n">
-        <v>39</v>
       </c>
       <c r="H13" t="n">
         <v>49</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="J13" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1279,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1073.5418</v>
+        <v>1074.5467</v>
       </c>
       <c r="Q13" t="n">
-        <v>94.94</v>
+        <v>94.91</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H14" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J14" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1341,13 +1341,13 @@
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>1067.6137</v>
+        <v>1074.0959</v>
       </c>
       <c r="Q14" t="n">
-        <v>94.75</v>
+        <v>94.89</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1373,25 +1373,25 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F15" t="n">
         <v>34</v>
       </c>
       <c r="G15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H15" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
@@ -1409,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1064.0483</v>
+        <v>1067.7894</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.63</v>
+        <v>94.69</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1438,25 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
         <v>38</v>
       </c>
       <c r="H16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1474,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1063.6903</v>
+        <v>1063.1545</v>
       </c>
       <c r="Q16" t="n">
-        <v>94.62</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
@@ -1515,13 +1515,13 @@
         <v>38</v>
       </c>
       <c r="H17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="J17" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -1539,10 +1539,10 @@
         <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>1063.5943</v>
+        <v>1061.8874</v>
       </c>
       <c r="Q17" t="n">
-        <v>94.62</v>
+        <v>94.5</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1604,10 +1604,10 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>1060.8781</v>
+        <v>1061.1692</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.53</v>
+        <v>94.47</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1633,25 +1633,25 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H19" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I19" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -1669,10 +1669,10 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>1060.6875</v>
+        <v>1061.0489</v>
       </c>
       <c r="Q19" t="n">
-        <v>94.52</v>
+        <v>94.47</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H20" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
@@ -1734,10 +1734,10 @@
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>1058.9128</v>
+        <v>1059.9455</v>
       </c>
       <c r="Q20" t="n">
-        <v>94.47</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1760,28 +1760,28 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H21" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
@@ -1799,10 +1799,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1058.2904</v>
+        <v>1059.727</v>
       </c>
       <c r="Q21" t="n">
-        <v>94.45</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -1936,28 +1936,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
         <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -1972,10 +1972,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>1085.3362</v>
+        <v>1085.8226</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2001,28 +2001,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
         <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2037,13 +2037,13 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1083.0127</v>
+        <v>1085.7483</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.93000000000001</v>
+        <v>95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2066,28 +2066,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H4" t="n">
         <v>45</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2102,13 +2102,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>1080.4242</v>
+        <v>1085.0111</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.84</v>
+        <v>94.97</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2131,28 +2131,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J5" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -2167,13 +2167,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>1077.5757</v>
+        <v>1084.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.75</v>
+        <v>94.95</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2196,28 +2196,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -2232,13 +2232,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1076.7101</v>
+        <v>1082.4713</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.72</v>
+        <v>94.89</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2261,28 +2261,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
+        <v>26</v>
+      </c>
+      <c r="G7" t="n">
         <v>31</v>
       </c>
-      <c r="G7" t="n">
-        <v>41</v>
-      </c>
       <c r="H7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I7" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -2300,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1075.9632</v>
+        <v>1080.4438</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.7</v>
+        <v>94.83</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2326,28 +2326,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" t="n">
         <v>24</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -2365,10 +2365,10 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1075.7471</v>
+        <v>1080.0368</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.69</v>
+        <v>94.81</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2391,28 +2391,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="H9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J9" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -2430,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1074.3567</v>
+        <v>1079.3732</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.65000000000001</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2456,28 +2456,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" t="n">
         <v>19</v>
       </c>
-      <c r="E10" t="n">
-        <v>24</v>
-      </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H10" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I10" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1072.873</v>
+        <v>1079.2948</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.59999999999999</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H11" t="n">
         <v>40</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="J11" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -2560,10 +2560,10 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1071.9097</v>
+        <v>1078.208</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.56999999999999</v>
+        <v>94.75</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:45</t>
+          <t>2026-05-27 14:49:16</t>
         </is>
       </c>
     </row>
@@ -2697,28 +2697,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
         <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1075.2819</v>
+        <v>1077.37</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -2762,28 +2762,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
         <v>24</v>
       </c>
       <c r="F3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G3" t="n">
         <v>34</v>
-      </c>
-      <c r="G3" t="n">
-        <v>39</v>
       </c>
       <c r="H3" t="n">
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="J3" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2801,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1073.5418</v>
+        <v>1074.5467</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.94</v>
+        <v>94.91</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -2827,28 +2827,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2863,13 +2863,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1067.6137</v>
+        <v>1074.0959</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.75</v>
+        <v>94.89</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -2895,25 +2895,25 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="J5" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -2931,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1064.0483</v>
+        <v>1067.7894</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.63</v>
+        <v>94.69</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -2960,25 +2960,25 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
         <v>38</v>
       </c>
       <c r="H6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I6" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1063.6903</v>
+        <v>1063.1545</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.62</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
@@ -3037,13 +3037,13 @@
         <v>38</v>
       </c>
       <c r="H7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="J7" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -3061,10 +3061,10 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>1063.5943</v>
+        <v>1061.8874</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.62</v>
+        <v>94.5</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -3126,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1060.8781</v>
+        <v>1061.1692</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.53</v>
+        <v>94.47</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -3155,25 +3155,25 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H9" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -3191,10 +3191,10 @@
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1060.6875</v>
+        <v>1061.0489</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.52</v>
+        <v>94.47</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -3217,28 +3217,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H10" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="I10" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -3256,10 +3256,10 @@
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1058.9128</v>
+        <v>1059.9455</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.47</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>
@@ -3282,28 +3282,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H11" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -3321,10 +3321,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1058.2904</v>
+        <v>1059.727</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.45</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:47</t>
+          <t>2026-05-27 14:49:19</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/uk49s_predictions.xlsx
+++ b/data/exports/predictions/uk49s_predictions.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:16</t>
+          <t>2026-05-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:49:19</t>
+          <t>2026-05-28 08:47:35</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/uk49s_predictions.xlsx
+++ b/data/exports/predictions/uk49s_predictions.xlsx
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -561,10 +561,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1085.8226</v>
+        <v>1090.3221</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -576,7 +576,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H3" t="n">
         <v>44</v>
-      </c>
-      <c r="H3" t="n">
-        <v>49</v>
       </c>
       <c r="I3" t="n">
         <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -629,10 +629,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1085.7483</v>
+        <v>1088.6322</v>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>94.95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
         <v>19</v>
       </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
         <v>44</v>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -691,13 +691,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1085.0111</v>
+        <v>1088.1984</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.97</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -720,28 +720,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I5" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -756,13 +756,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>1084.24</v>
+        <v>1086.7156</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.95</v>
+        <v>94.88</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H6" t="n">
         <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="J6" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -821,13 +821,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1082.4713</v>
+        <v>1085.4744</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.89</v>
+        <v>94.84</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>19</v>
@@ -865,13 +865,13 @@
         <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -889,10 +889,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1080.4438</v>
+        <v>1084.2963</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.83</v>
+        <v>94.81</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -951,13 +951,13 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1080.0368</v>
+        <v>1083.5867</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.81</v>
+        <v>94.78</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -980,28 +980,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I9" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -1016,13 +1016,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1079.3732</v>
+        <v>1081.6518</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.79000000000001</v>
+        <v>94.72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -1045,25 +1045,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>163</v>
@@ -1084,10 +1084,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1079.2948</v>
+        <v>1081.3515</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.79000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -1110,28 +1110,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>41</v>
+      </c>
+      <c r="H11" t="n">
+        <v>44</v>
+      </c>
+      <c r="I11" t="n">
         <v>30</v>
       </c>
-      <c r="G11" t="n">
-        <v>31</v>
-      </c>
-      <c r="H11" t="n">
-        <v>40</v>
-      </c>
-      <c r="I11" t="n">
-        <v>41</v>
-      </c>
       <c r="J11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -1146,13 +1146,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1078.208</v>
+        <v>1080.2544</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.75</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
         <v>49</v>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J12" t="n">
         <v>165</v>
@@ -1214,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1077.37</v>
+        <v>1081.3681</v>
       </c>
       <c r="Q12" t="n">
         <v>95</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H13" t="n">
         <v>49</v>
       </c>
       <c r="I13" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="K13" t="n">
         <v>3</v>
@@ -1276,13 +1276,13 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>1074.5467</v>
+        <v>1077.2259</v>
       </c>
       <c r="Q13" t="n">
-        <v>94.91</v>
+        <v>94.87</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H14" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1341,13 +1341,13 @@
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1074.0959</v>
+        <v>1073.3679</v>
       </c>
       <c r="Q14" t="n">
-        <v>94.89</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1376,22 +1376,22 @@
         <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H15" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J15" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K15" t="n">
         <v>3</v>
@@ -1409,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1067.7894</v>
+        <v>1073.2263</v>
       </c>
       <c r="Q15" t="n">
-        <v>94.69</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1441,22 +1441,22 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1471,13 +1471,13 @@
         <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>1063.1545</v>
+        <v>1071.7913</v>
       </c>
       <c r="Q16" t="n">
-        <v>94.54000000000001</v>
+        <v>94.69</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1503,25 +1503,25 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H17" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I17" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J17" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -1536,13 +1536,13 @@
         <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1061.8874</v>
+        <v>1070.9496</v>
       </c>
       <c r="Q17" t="n">
-        <v>94.5</v>
+        <v>94.66</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H18" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
@@ -1601,13 +1601,13 @@
         <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1061.1692</v>
+        <v>1068.1441</v>
       </c>
       <c r="Q18" t="n">
-        <v>94.47</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1633,25 +1633,25 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
+        <v>32</v>
+      </c>
+      <c r="G19" t="n">
         <v>38</v>
-      </c>
-      <c r="G19" t="n">
-        <v>44</v>
       </c>
       <c r="H19" t="n">
         <v>49</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -1666,13 +1666,13 @@
         <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1061.0489</v>
+        <v>1068.0878</v>
       </c>
       <c r="Q19" t="n">
-        <v>94.47</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="J20" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
@@ -1734,10 +1734,10 @@
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>1059.9455</v>
+        <v>1066.4108</v>
       </c>
       <c r="Q20" t="n">
-        <v>94.43000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1760,25 +1760,25 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
         <v>11</v>
       </c>
-      <c r="E21" t="n">
-        <v>20</v>
-      </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H21" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>149</v>
@@ -1796,13 +1796,13 @@
         <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>1059.727</v>
+        <v>1065.5983</v>
       </c>
       <c r="Q21" t="n">
-        <v>94.43000000000001</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -1936,28 +1936,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H2" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -1972,10 +1972,10 @@
         <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1085.8226</v>
+        <v>1090.3221</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2001,28 +2001,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
+        <v>41</v>
+      </c>
+      <c r="H3" t="n">
         <v>44</v>
-      </c>
-      <c r="H3" t="n">
-        <v>49</v>
       </c>
       <c r="I3" t="n">
         <v>26</v>
       </c>
       <c r="J3" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2040,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1085.7483</v>
+        <v>1088.6322</v>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>94.95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2066,28 +2066,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
         <v>19</v>
       </c>
-      <c r="E4" t="n">
-        <v>20</v>
-      </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
         <v>44</v>
       </c>
       <c r="H4" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J4" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2102,13 +2102,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1085.0111</v>
+        <v>1088.1984</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.97</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2131,28 +2131,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I5" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -2167,13 +2167,13 @@
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>1084.24</v>
+        <v>1086.7156</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.95</v>
+        <v>94.88</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2196,28 +2196,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H6" t="n">
         <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="J6" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -2232,13 +2232,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1082.4713</v>
+        <v>1085.4744</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.89</v>
+        <v>94.84</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>19</v>
@@ -2276,13 +2276,13 @@
         <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -2300,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1080.4438</v>
+        <v>1084.2963</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.83</v>
+        <v>94.81</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2326,28 +2326,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -2362,13 +2362,13 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>1080.0368</v>
+        <v>1083.5867</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.81</v>
+        <v>94.78</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2391,28 +2391,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I9" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -2427,13 +2427,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>1079.3732</v>
+        <v>1081.6518</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.79000000000001</v>
+        <v>94.72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2456,25 +2456,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G10" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>163</v>
@@ -2495,10 +2495,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1079.2948</v>
+        <v>1081.3515</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.79000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>24</v>
       </c>
       <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>41</v>
+      </c>
+      <c r="H11" t="n">
+        <v>44</v>
+      </c>
+      <c r="I11" t="n">
         <v>30</v>
       </c>
-      <c r="G11" t="n">
-        <v>31</v>
-      </c>
-      <c r="H11" t="n">
-        <v>40</v>
-      </c>
-      <c r="I11" t="n">
-        <v>41</v>
-      </c>
       <c r="J11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -2557,13 +2557,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1078.208</v>
+        <v>1080.2544</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.75</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:33</t>
+          <t>2026-05-28 17:13:25</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
         <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
         <v>165</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1077.37</v>
+        <v>1081.3681</v>
       </c>
       <c r="Q2" t="n">
         <v>95</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -2762,28 +2762,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H3" t="n">
         <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -2798,13 +2798,13 @@
         <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1074.5467</v>
+        <v>1077.2259</v>
       </c>
       <c r="Q3" t="n">
-        <v>94.91</v>
+        <v>94.87</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -2827,28 +2827,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H4" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -2863,13 +2863,13 @@
         <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1074.0959</v>
+        <v>1073.3679</v>
       </c>
       <c r="Q4" t="n">
-        <v>94.89</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -2898,22 +2898,22 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J5" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -2931,10 +2931,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1067.7894</v>
+        <v>1073.2263</v>
       </c>
       <c r="Q5" t="n">
-        <v>94.69</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -2963,22 +2963,22 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H6" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -2993,13 +2993,13 @@
         <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1063.1545</v>
+        <v>1071.7913</v>
       </c>
       <c r="Q6" t="n">
-        <v>94.54000000000001</v>
+        <v>94.69</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -3025,25 +3025,25 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J7" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -3058,13 +3058,13 @@
         <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1061.8874</v>
+        <v>1070.9496</v>
       </c>
       <c r="Q7" t="n">
-        <v>94.5</v>
+        <v>94.66</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -3087,28 +3087,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H8" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -3123,13 +3123,13 @@
         <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1061.1692</v>
+        <v>1068.1441</v>
       </c>
       <c r="Q8" t="n">
-        <v>94.47</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -3155,25 +3155,25 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
+        <v>32</v>
+      </c>
+      <c r="G9" t="n">
         <v>38</v>
-      </c>
-      <c r="G9" t="n">
-        <v>44</v>
       </c>
       <c r="H9" t="n">
         <v>49</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
@@ -3188,13 +3188,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1061.0489</v>
+        <v>1068.0878</v>
       </c>
       <c r="Q9" t="n">
-        <v>94.47</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -3217,28 +3217,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="J10" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -3256,10 +3256,10 @@
         <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>1059.9455</v>
+        <v>1066.4108</v>
       </c>
       <c r="Q10" t="n">
-        <v>94.43000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>
@@ -3282,25 +3282,25 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
         <v>11</v>
       </c>
-      <c r="E11" t="n">
-        <v>20</v>
-      </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H11" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>149</v>
@@ -3318,13 +3318,13 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>1059.727</v>
+        <v>1065.5983</v>
       </c>
       <c r="Q11" t="n">
-        <v>94.43000000000001</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:35</t>
+          <t>2026-05-28 17:13:28</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/uk49s_predictions.xlsx
+++ b/data/exports/predictions/uk49s_predictions.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:08</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:08</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:08</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:25</t>
+          <t>2026-05-28 19:43:05</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:07</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:08</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:08</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:28</t>
+          <t>2026-05-28 19:43:08</t>
         </is>
       </c>
     </row>
